--- a/ig/DM-MARS-2026/ValueSet-JDV-J20-ChampActivite-ROR.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J20-ChampActivite-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20231030120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-30T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,6 +127,12 @@
   </si>
   <si>
     <t>Ville</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Social</t>
   </si>
   <si>
     <t/>
@@ -397,7 +403,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -457,15 +463,23 @@
         <v>38</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
